--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.96033608961836</v>
+        <v>8.118554614562983</v>
       </c>
       <c r="D2" t="n">
-        <v>16.61932314969485</v>
+        <v>2.700640011825413</v>
       </c>
       <c r="E2" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F2" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.22075103122179</v>
+        <v>4.098372042573541</v>
       </c>
       <c r="D3" t="n">
-        <v>29.56346456333652</v>
+        <v>4.804062991542184</v>
       </c>
       <c r="E3" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F3" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.42377029385137</v>
+        <v>6.406362672750848</v>
       </c>
       <c r="D4" t="n">
-        <v>10.56626370745826</v>
+        <v>1.717017852461967</v>
       </c>
       <c r="E4" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F4" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.03183036214424</v>
+        <v>2.442672433848438</v>
       </c>
       <c r="D5" t="n">
-        <v>17.48183351120758</v>
+        <v>2.840797945571231</v>
       </c>
       <c r="E5" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F5" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.75669724228068</v>
+        <v>4.18546330187061</v>
       </c>
       <c r="D6" t="n">
-        <v>9.618964736349977</v>
+        <v>1.563081769656871</v>
       </c>
       <c r="E6" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F6" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.42512486025331</v>
+        <v>3.644082789791163</v>
       </c>
       <c r="D7" t="n">
-        <v>22.1592118517134</v>
+        <v>3.600871925903428</v>
       </c>
       <c r="E7" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F7" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.9161665588535</v>
+        <v>6.973877065813694</v>
       </c>
       <c r="D8" t="n">
-        <v>42.42090133709672</v>
+        <v>6.893396467278218</v>
       </c>
       <c r="E8" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F8" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.36542974023084</v>
+        <v>8.509382332787512</v>
       </c>
       <c r="D9" t="n">
-        <v>51.80782968991105</v>
+        <v>8.418772324610545</v>
       </c>
       <c r="E9" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F9" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.04223124621483</v>
+        <v>2.606862577509909</v>
       </c>
       <c r="D10" t="n">
-        <v>15.77960236032713</v>
+        <v>2.564185383553158</v>
       </c>
       <c r="E10" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F10" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>11.7366075336385</v>
+        <v>1.907198724216256</v>
       </c>
       <c r="D11" t="n">
-        <v>4.261728204102242</v>
+        <v>0.6925308331666142</v>
       </c>
       <c r="E11" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F11" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20.48935151606783</v>
+        <v>3.329519621361023</v>
       </c>
       <c r="D12" t="n">
-        <v>21.17443936203743</v>
+        <v>3.440846396331082</v>
       </c>
       <c r="E12" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F12" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>4.363962948968529</v>
+        <v>0.709143979207386</v>
       </c>
       <c r="D13" t="n">
-        <v>4.953781737909021</v>
+        <v>0.804989532410216</v>
       </c>
       <c r="E13" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F13" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6.791172087296571</v>
+        <v>1.103565464185693</v>
       </c>
       <c r="D14" t="n">
-        <v>2.874843411256437</v>
+        <v>0.467162054329171</v>
       </c>
       <c r="E14" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F14" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>12.99757131697629</v>
+        <v>2.112105339008648</v>
       </c>
       <c r="D15" t="n">
-        <v>12.91747041535628</v>
+        <v>2.099088942495395</v>
       </c>
       <c r="E15" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F15" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>23.79901960389483</v>
+        <v>3.86734068563291</v>
       </c>
       <c r="D16" t="n">
-        <v>16.72743809853926</v>
+        <v>2.718208691012629</v>
       </c>
       <c r="E16" t="n">
-        <v>14.57119861012618</v>
+        <v>2.367819774145504</v>
       </c>
       <c r="F16" t="n">
-        <v>13.27378279556664</v>
+        <v>2.156989704279578</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
